--- a/docs/requirements/요구사항_정의서.xlsx
+++ b/docs/requirements/요구사항_정의서.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항정의서" sheetId="1" r:id="R05ef246df2ef4035"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례·작성안내" sheetId="2" r:id="Rfc64a521fae8471e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항정의서" sheetId="1" r:id="Rd405d943cc0d4833"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례·작성안내" sheetId="2" r:id="Rbdb6ee933b28465a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2731,14 +2731,13 @@
         <x:v>업로드 계약서와 대화 이력은 검토 후 서버에 영구 저장하지 않는다.</x:v>
       </x:c>
       <x:c r="E61" s="17" t="str">
-        <x:v>임시 저장소에서만 처리하고 정상 완료, 실패, 취소 후 즉시 삭제를 시도한다. 비정상 종료에 대비해 배포 설정으로 관리하는 최대 보존 시간 TTL을 적용하고, 서버 시작 또는 정기 정리 작업으로 잔존 임시 파일을 제거한다. 임시 저장소는 백업 대상에서 제외한다.</x:v>
+        <x:v>재시도할 수 없는 실패는 즉시 삭제한다. 검토 완료 후에는 결과 페이지 이용 중 유지하고, 페이지 이탈·새 검토 시작·명시적 종료 시 삭제 요청한다. 요청 누락은 세션 생성 시점부터 1시간 TTL로 삭제하며, 세션 만료 시 EXPIRED 처리 후 파일과 결과를 삭제한다.</x:v>
       </x:c>
       <x:c r="F61" s="7" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="G61" s="30" t="str">
-        <x:v>TLS는 전송 구간을 보호하지만, 저장·로그 보호를 대체하지 않음. 임시 파일 위치, TTL 설정값, 정상/실패/취소 시 삭제, 컨테이너 재시작 후 잔존 파일 청소 방식을 배포 설계에 확정해야 한다.
-[MCP 명세 검토] 임시 저장·삭제·TTL·백업 제외는 서버/인프라 운영 정책이며 MCP 명세에 없음.</x:v>
+        <x:v>세션 및 임시 파일 TTL은 세션 생성 시점부터 1시간으로 확정한다.</x:v>
       </x:c>
       <x:c r="H61" s="14" t="str">
         <x:v>미포함</x:v>
@@ -2935,7 +2934,7 @@
         <x:v>사용자별 요청, 임시 파일, 검토 결과를 격리한다.</x:v>
       </x:c>
       <x:c r="E67" s="17" t="str">
-        <x:v>다른 브라우저 세션이나 사용자가 계약서, 진행 상태, 결과, 대화 이력에 접근할 수 없도록 세션 또는 인증 단위 권한 검사를 수행한다.</x:v>
+        <x:v>로그인 없이 서버가 발급한 세션 토큰으로 사용자별 요청·파일·결과를 격리한다.</x:v>
       </x:c>
       <x:c r="F67" s="7" t="str">
         <x:v>MVP</x:v>
@@ -2969,14 +2968,13 @@
         <x:v>업로드 크기와 요청 빈도를 제한한다.</x:v>
       </x:c>
       <x:c r="E68" s="17" t="str">
-        <x:v>허용 파일 크기, 사용자 또는 IP별 동시 검토 수, 시간당 요청 수를 제한하고 초과 시 명확한 안내를 표시한다.</x:v>
+        <x:v>허용 파일 크기는 10MB, 동시 검토 수는 2건으로 제한한다.</x:v>
       </x:c>
       <x:c r="F68" s="7" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="G68" s="30" t="str">
-        <x:v>최대 파일 크기와 동시성 기준을 성능 테스트 후 확정 필요.
-[MCP 명세 검토] 파일 크기·동시성·요청 빈도 제한 입력 또는 오류 스키마가 없음. 게이트웨이·백엔드 제한값과 성능 테스트로 확정 필요.</x:v>
+        <x:v>최대 파일 크기 10MB, 동시 검토 수 2건으로 확정한다.</x:v>
       </x:c>
       <x:c r="H68" s="14" t="str">
         <x:v>미포함</x:v>

--- a/docs/requirements/요구사항_정의서.xlsx
+++ b/docs/requirements/요구사항_정의서.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항정의서" sheetId="1" r:id="Rd405d943cc0d4833"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례·작성안내" sheetId="2" r:id="Rbdb6ee933b28465a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항정의서" sheetId="1" r:id="R64a151f4e2284f6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례·작성안내" sheetId="2" r:id="Rf31f014977a047a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2731,13 +2731,13 @@
         <x:v>업로드 계약서와 대화 이력은 검토 후 서버에 영구 저장하지 않는다.</x:v>
       </x:c>
       <x:c r="E61" s="17" t="str">
-        <x:v>재시도할 수 없는 실패는 즉시 삭제한다. 검토 완료 후에는 결과 페이지 이용 중 유지하고, 페이지 이탈·새 검토 시작·명시적 종료 시 삭제 요청한다. 요청 누락은 세션 생성 시점부터 1시간 TTL로 삭제하며, 세션 만료 시 EXPIRED 처리 후 파일과 결과를 삭제한다.</x:v>
+        <x:v>재시도할 수 없는 실패는 즉시 삭제한다. 검토 완료 후에는 결과 페이지 이용 중 유지하고, 페이지 이탈·새 검토 시작·명시적 종료 시 삭제 요청한다. 요청 누락은 마지막 사용자 액션 후 30분 TTL로 삭제하며, 검토 진행 중에는 완료 전까지 세션을 만료시키지 않는다. 세션 만료 시 EXPIRED 처리 후 파일과 결과를 삭제한다.</x:v>
       </x:c>
       <x:c r="F61" s="7" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="G61" s="30" t="str">
-        <x:v>세션 및 임시 파일 TTL은 세션 생성 시점부터 1시간으로 확정한다.</x:v>
+        <x:v>세션 및 임시 파일 TTL은 마지막 사용자 액션 후 30분으로 확정한다.</x:v>
       </x:c>
       <x:c r="H61" s="14" t="str">
         <x:v>미포함</x:v>
@@ -2974,7 +2974,7 @@
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="G68" s="30" t="str">
-        <x:v>최대 파일 크기 10MB, 동시 검토 수 2건으로 확정한다.</x:v>
+        <x:v>최대 파일 크기 10MB, 동시 검토 수 2건, 세션 TTL은 마지막 사용자 액션 후 30분으로 확정한다.</x:v>
       </x:c>
       <x:c r="H68" s="14" t="str">
         <x:v>미포함</x:v>
